--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/144.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/144.xlsx
@@ -426,13 +426,13 @@
         <v>-15.22728250323304</v>
       </c>
       <c r="E2">
-        <v>-19.29975148188164</v>
+        <v>-16.56008357740317</v>
       </c>
       <c r="F2">
-        <v>3.484491712830292</v>
+        <v>4.418762574608103</v>
       </c>
       <c r="G2">
-        <v>-8.385146214721214</v>
+        <v>-6.871617762895055</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.20865386423392</v>
       </c>
       <c r="E3">
-        <v>-19.35025755248919</v>
+        <v>-16.69452038526888</v>
       </c>
       <c r="F3">
-        <v>3.441448085846024</v>
+        <v>4.441642082273426</v>
       </c>
       <c r="G3">
-        <v>-7.805482932976986</v>
+        <v>-6.723599961288701</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.19838917252884</v>
       </c>
       <c r="E4">
-        <v>-20.50574298028635</v>
+        <v>-17.23586775356782</v>
       </c>
       <c r="F4">
-        <v>3.635158489521078</v>
+        <v>4.386154720164304</v>
       </c>
       <c r="G4">
-        <v>-7.597858758936054</v>
+        <v>-6.972347732018459</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-15.18940066671036</v>
       </c>
       <c r="E5">
-        <v>-21.40402466986987</v>
+        <v>-19.25452561196703</v>
       </c>
       <c r="F5">
-        <v>3.773341769451674</v>
+        <v>4.621273553570498</v>
       </c>
       <c r="G5">
-        <v>-7.631050288512787</v>
+        <v>-6.283605285300785</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.17103571479504</v>
       </c>
       <c r="E6">
-        <v>-21.18873195859721</v>
+        <v>-19.76925461004889</v>
       </c>
       <c r="F6">
-        <v>3.442046167110846</v>
+        <v>4.876023037688237</v>
       </c>
       <c r="G6">
-        <v>-6.659252887641887</v>
+        <v>-5.880486776074812</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.12807628630834</v>
       </c>
       <c r="E7">
-        <v>-22.13252481195781</v>
+        <v>-20.04605758376773</v>
       </c>
       <c r="F7">
-        <v>3.646082998829197</v>
+        <v>4.559109550194813</v>
       </c>
       <c r="G7">
-        <v>-6.79737215808582</v>
+        <v>-5.128572499376765</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.0352206221153</v>
       </c>
       <c r="E8">
-        <v>-22.39964137977425</v>
+        <v>-20.4826296489512</v>
       </c>
       <c r="F8">
-        <v>3.928716986459972</v>
+        <v>4.787425830489218</v>
       </c>
       <c r="G8">
-        <v>-6.746926065158406</v>
+        <v>-5.020052816599455</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.86415180201781</v>
       </c>
       <c r="E9">
-        <v>-23.36567356898652</v>
+        <v>-20.13578476775572</v>
       </c>
       <c r="F9">
-        <v>3.847754013245154</v>
+        <v>4.760992626665885</v>
       </c>
       <c r="G9">
-        <v>-6.167100566682754</v>
+        <v>-4.111745058080698</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.59147970404823</v>
       </c>
       <c r="E10">
-        <v>-24.40439682296992</v>
+        <v>-22.79949657770353</v>
       </c>
       <c r="F10">
-        <v>3.934354855003425</v>
+        <v>4.981277056622747</v>
       </c>
       <c r="G10">
-        <v>-5.103872519108262</v>
+        <v>-2.866817718583307</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-14.19273264825833</v>
       </c>
       <c r="E11">
-        <v>-25.43973730686958</v>
+        <v>-23.54457093465954</v>
       </c>
       <c r="F11">
-        <v>3.995196784004243</v>
+        <v>4.730526930325725</v>
       </c>
       <c r="G11">
-        <v>-4.898857054952276</v>
+        <v>-3.500340265705938</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-13.66269610141238</v>
       </c>
       <c r="E12">
-        <v>-25.63609646831618</v>
+        <v>-23.27004125489254</v>
       </c>
       <c r="F12">
-        <v>4.044416718343784</v>
+        <v>5.346476080025353</v>
       </c>
       <c r="G12">
-        <v>-4.528658610568815</v>
+        <v>-3.372063247150258</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.98554617549661</v>
       </c>
       <c r="E13">
-        <v>-26.36727293854265</v>
+        <v>-25.08899340955349</v>
       </c>
       <c r="F13">
-        <v>4.329159729382087</v>
+        <v>5.052475234893365</v>
       </c>
       <c r="G13">
-        <v>-4.18186903369354</v>
+        <v>-1.089865847651802</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-12.17141656537353</v>
       </c>
       <c r="E14">
-        <v>-27.25056537916078</v>
+        <v>-25.63501416302834</v>
       </c>
       <c r="F14">
-        <v>4.702750114575053</v>
+        <v>5.484487059536169</v>
       </c>
       <c r="G14">
-        <v>-4.251208410013575</v>
+        <v>-0.3870304085734498</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.21522478433786</v>
       </c>
       <c r="E15">
-        <v>-28.97696458205296</v>
+        <v>-25.67759087564846</v>
       </c>
       <c r="F15">
-        <v>4.994665130586792</v>
+        <v>5.501221737807524</v>
       </c>
       <c r="G15">
-        <v>-3.020635595974464</v>
+        <v>-0.5452579326229162</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.14314575500573</v>
       </c>
       <c r="E16">
-        <v>-29.74686403351902</v>
+        <v>-27.84778958824036</v>
       </c>
       <c r="F16">
-        <v>4.732548146788556</v>
+        <v>6.152631639286193</v>
       </c>
       <c r="G16">
-        <v>-2.541695662262563</v>
+        <v>-0.9702757005911691</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.972800328680103</v>
       </c>
       <c r="E17">
-        <v>-30.25725022502752</v>
+        <v>-29.03173194670173</v>
       </c>
       <c r="F17">
-        <v>5.279573815105654</v>
+        <v>6.445083437374947</v>
       </c>
       <c r="G17">
-        <v>-2.414239659000622</v>
+        <v>-0.2818212713354115</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.754573697350592</v>
       </c>
       <c r="E18">
-        <v>-29.95361604281322</v>
+        <v>-29.02342219689765</v>
       </c>
       <c r="F18">
-        <v>5.26169433308363</v>
+        <v>6.471074293005185</v>
       </c>
       <c r="G18">
-        <v>-2.535571153014911</v>
+        <v>0.6655939616387561</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.53100235243915</v>
       </c>
       <c r="E19">
-        <v>-30.65466004699265</v>
+        <v>-29.77412318280819</v>
       </c>
       <c r="F19">
-        <v>5.686772722565002</v>
+        <v>7.07803896985405</v>
       </c>
       <c r="G19">
-        <v>-2.414001299721794</v>
+        <v>1.000697312760404</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.366035135447615</v>
       </c>
       <c r="E20">
-        <v>-31.94714539894387</v>
+        <v>-30.58320072715161</v>
       </c>
       <c r="F20">
-        <v>5.930130498159441</v>
+        <v>7.224176233586327</v>
       </c>
       <c r="G20">
-        <v>-1.813210116345938</v>
+        <v>1.302433675391736</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.306877176261246</v>
       </c>
       <c r="E21">
-        <v>-32.53124609034923</v>
+        <v>-32.22935310639087</v>
       </c>
       <c r="F21">
-        <v>6.153456693219382</v>
+        <v>7.405094987827351</v>
       </c>
       <c r="G21">
-        <v>-1.539375031519582</v>
+        <v>1.086351057497967</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.404205818943739</v>
       </c>
       <c r="E22">
-        <v>-33.05769930763694</v>
+        <v>-30.4556109719855</v>
       </c>
       <c r="F22">
-        <v>5.938271692994154</v>
+        <v>7.721928952050106</v>
       </c>
       <c r="G22">
-        <v>-0.8751835905211435</v>
+        <v>1.942295917222072</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.684312137552475</v>
       </c>
       <c r="E23">
-        <v>-33.31484643992549</v>
+        <v>-30.6001349557033</v>
       </c>
       <c r="F23">
-        <v>6.244618525897467</v>
+        <v>7.16953049275845</v>
       </c>
       <c r="G23">
-        <v>-0.2087078731006074</v>
+        <v>1.129275590960157</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.164187610855085</v>
       </c>
       <c r="E24">
-        <v>-33.2291835613594</v>
+        <v>-31.54188320304944</v>
       </c>
       <c r="F24">
-        <v>6.313071494595207</v>
+        <v>7.264825878776505</v>
       </c>
       <c r="G24">
-        <v>-1.482701802432799</v>
+        <v>1.663723441729019</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.838272618633073</v>
       </c>
       <c r="E25">
-        <v>-33.32120668166927</v>
+        <v>-31.48773397510272</v>
       </c>
       <c r="F25">
-        <v>6.622002833795255</v>
+        <v>7.241820459265957</v>
       </c>
       <c r="G25">
-        <v>-0.6840889703577927</v>
+        <v>2.23460384615756</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.689511794189979</v>
       </c>
       <c r="E26">
-        <v>-33.63731001706368</v>
+        <v>-31.10507565721757</v>
       </c>
       <c r="F26">
-        <v>6.372351122674345</v>
+        <v>6.461889355242944</v>
       </c>
       <c r="G26">
-        <v>-0.4383935226152423</v>
+        <v>1.904582182438694</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.687220057159196</v>
       </c>
       <c r="E27">
-        <v>-33.35076855999134</v>
+        <v>-31.51276964365412</v>
       </c>
       <c r="F27">
-        <v>6.297759951521861</v>
+        <v>6.850812821061729</v>
       </c>
       <c r="G27">
-        <v>-0.9464132883441023</v>
+        <v>1.851762428359622</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.794441522819121</v>
       </c>
       <c r="E28">
-        <v>-32.77360549076573</v>
+        <v>-31.47241867600878</v>
       </c>
       <c r="F28">
-        <v>5.814400945049127</v>
+        <v>7.31096097290802</v>
       </c>
       <c r="G28">
-        <v>-1.052661936881472</v>
+        <v>2.234888553073938</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.973616707627771</v>
       </c>
       <c r="E29">
-        <v>-32.58786560086713</v>
+        <v>-31.38424249436842</v>
       </c>
       <c r="F29">
-        <v>6.00959081290558</v>
+        <v>6.956209319189521</v>
       </c>
       <c r="G29">
-        <v>-1.503074899681474</v>
+        <v>2.357044372927505</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.190483532710935</v>
       </c>
       <c r="E30">
-        <v>-32.16388722189899</v>
+        <v>-30.49732953878117</v>
       </c>
       <c r="F30">
-        <v>5.644434864607919</v>
+        <v>7.112119661540027</v>
       </c>
       <c r="G30">
-        <v>-1.593446171812499</v>
+        <v>1.967873192058481</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.41941566600337</v>
       </c>
       <c r="E31">
-        <v>-31.94915604140328</v>
+        <v>-31.53848231906968</v>
       </c>
       <c r="F31">
-        <v>5.947859217314155</v>
+        <v>7.133599228294618</v>
       </c>
       <c r="G31">
-        <v>-1.563419523771309</v>
+        <v>0.7042644440829828</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.643692340036986</v>
       </c>
       <c r="E32">
-        <v>-32.12402759368348</v>
+        <v>-29.5020751067974</v>
       </c>
       <c r="F32">
-        <v>5.954883772889896</v>
+        <v>6.690389533100771</v>
       </c>
       <c r="G32">
-        <v>-1.048272153496398</v>
+        <v>1.029532164407456</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.853822638869604</v>
       </c>
       <c r="E33">
-        <v>-31.29734334239823</v>
+        <v>-30.73435439681664</v>
       </c>
       <c r="F33">
-        <v>5.901826840740587</v>
+        <v>6.889159604872123</v>
       </c>
       <c r="G33">
-        <v>-2.424581803265305</v>
+        <v>0.4893338960368795</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.048720782559255</v>
       </c>
       <c r="E34">
-        <v>-31.42208015893951</v>
+        <v>-30.30294252776491</v>
       </c>
       <c r="F34">
-        <v>6.232019057700887</v>
+        <v>6.697364386632342</v>
       </c>
       <c r="G34">
-        <v>-1.934654168908562</v>
+        <v>1.087774592079853</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.229372145871907</v>
       </c>
       <c r="E35">
-        <v>-31.24378734454652</v>
+        <v>-29.29906135279653</v>
       </c>
       <c r="F35">
-        <v>6.230784790270715</v>
+        <v>7.126075995542394</v>
       </c>
       <c r="G35">
-        <v>-2.437628663235573</v>
+        <v>-0.05494958552915707</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.402872112095677</v>
       </c>
       <c r="E36">
-        <v>-30.2245342645591</v>
+        <v>-28.32658061659734</v>
       </c>
       <c r="F36">
-        <v>5.974448154209214</v>
+        <v>7.197186366868314</v>
       </c>
       <c r="G36">
-        <v>-3.493394741164547</v>
+        <v>0.6664613245700451</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.574189268123851</v>
       </c>
       <c r="E37">
-        <v>-30.40708837299331</v>
+        <v>-28.19193549892728</v>
       </c>
       <c r="F37">
-        <v>6.189793857710585</v>
+        <v>6.757059855147686</v>
       </c>
       <c r="G37">
-        <v>-2.933750328296292</v>
+        <v>0.6379045587482919</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.748920730786909</v>
       </c>
       <c r="E38">
-        <v>-28.99264668754152</v>
+        <v>-28.30175552208729</v>
       </c>
       <c r="F38">
-        <v>6.100144623910011</v>
+        <v>7.242249553580607</v>
       </c>
       <c r="G38">
-        <v>-3.251470004791227</v>
+        <v>0.4054016349797371</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.929348685929266</v>
       </c>
       <c r="E39">
-        <v>-28.2833427467721</v>
+        <v>-26.89647041107901</v>
       </c>
       <c r="F39">
-        <v>6.496679129425718</v>
+        <v>7.090716304586493</v>
       </c>
       <c r="G39">
-        <v>-3.345972837755262</v>
+        <v>-0.04505767545781477</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.116851209852625</v>
       </c>
       <c r="E40">
-        <v>-29.06074587966887</v>
+        <v>-26.82341253991326</v>
       </c>
       <c r="F40">
-        <v>6.464208783970783</v>
+        <v>7.592579382102963</v>
       </c>
       <c r="G40">
-        <v>-3.734319692785008</v>
+        <v>-0.4117303888419522</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.312917441557538</v>
       </c>
       <c r="E41">
-        <v>-28.28697911140026</v>
+        <v>-26.12705097785776</v>
       </c>
       <c r="F41">
-        <v>6.694282859893929</v>
+        <v>6.66465215789579</v>
       </c>
       <c r="G41">
-        <v>-3.804903834227809</v>
+        <v>-1.111788280212855</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.515592792938339</v>
       </c>
       <c r="E42">
-        <v>-27.35337985303092</v>
+        <v>-26.66770096115951</v>
       </c>
       <c r="F42">
-        <v>6.423792738388195</v>
+        <v>7.156796829042616</v>
       </c>
       <c r="G42">
-        <v>-3.339335193949023</v>
+        <v>-0.7393883230457786</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.725127023437504</v>
       </c>
       <c r="E43">
-        <v>-26.79437143610207</v>
+        <v>-26.50760129109234</v>
       </c>
       <c r="F43">
-        <v>6.825567496094011</v>
+        <v>7.182742952833101</v>
       </c>
       <c r="G43">
-        <v>-3.720213458242173</v>
+        <v>-0.9084214677354262</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.93634816817567</v>
       </c>
       <c r="E44">
-        <v>-26.70257021101858</v>
+        <v>-25.28440159145848</v>
       </c>
       <c r="F44">
-        <v>6.766895889688528</v>
+        <v>7.43248909783793</v>
       </c>
       <c r="G44">
-        <v>-4.241177457029583</v>
+        <v>-1.196220433646427</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.147324608040282</v>
       </c>
       <c r="E45">
-        <v>-24.78008808359426</v>
+        <v>-24.12910635956963</v>
       </c>
       <c r="F45">
-        <v>6.4477027351026</v>
+        <v>7.220364086798644</v>
       </c>
       <c r="G45">
-        <v>-3.983355480976683</v>
+        <v>-0.9647172946307327</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.350299304992849</v>
       </c>
       <c r="E46">
-        <v>-25.04652538030956</v>
+        <v>-22.94019626512184</v>
       </c>
       <c r="F46">
-        <v>6.731194911362675</v>
+        <v>7.574779423351607</v>
       </c>
       <c r="G46">
-        <v>-4.155626339203738</v>
+        <v>-0.6082443720530898</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.542887320284197</v>
       </c>
       <c r="E47">
-        <v>-25.36814666128232</v>
+        <v>-23.04528856141785</v>
       </c>
       <c r="F47">
-        <v>6.723834038621398</v>
+        <v>7.52540375594034</v>
       </c>
       <c r="G47">
-        <v>-3.744085802125858</v>
+        <v>-1.358864225445282</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.716932397867713</v>
       </c>
       <c r="E48">
-        <v>-23.79114634437719</v>
+        <v>-22.98417680468434</v>
       </c>
       <c r="F48">
-        <v>6.839432709682069</v>
+        <v>7.523738737460713</v>
       </c>
       <c r="G48">
-        <v>-4.434625875071356</v>
+        <v>-1.04285941153969</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.872936303239715</v>
       </c>
       <c r="E49">
-        <v>-23.55365052504492</v>
+        <v>-21.03663410210158</v>
       </c>
       <c r="F49">
-        <v>7.021542656248318</v>
+        <v>7.105356870063572</v>
       </c>
       <c r="G49">
-        <v>-3.762250765499839</v>
+        <v>-1.959046268441912</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.006871510612664</v>
       </c>
       <c r="E50">
-        <v>-23.43027677917995</v>
+        <v>-21.50808900256613</v>
       </c>
       <c r="F50">
-        <v>6.815671819100168</v>
+        <v>7.538135762921368</v>
       </c>
       <c r="G50">
-        <v>-3.714360413728742</v>
+        <v>-1.589953546268568</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.124640651370145</v>
       </c>
       <c r="E51">
-        <v>-22.43918401480923</v>
+        <v>-22.3547415599882</v>
       </c>
       <c r="F51">
-        <v>6.623649628192021</v>
+        <v>7.416407173079981</v>
       </c>
       <c r="G51">
-        <v>-5.123110099236967</v>
+        <v>-1.381164060197812</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.227991210603081</v>
       </c>
       <c r="E52">
-        <v>-22.13735216524998</v>
+        <v>-20.9414138791423</v>
       </c>
       <c r="F52">
-        <v>6.543622710142365</v>
+        <v>7.901292032308671</v>
       </c>
       <c r="G52">
-        <v>-4.35570909050621</v>
+        <v>-2.3297611579295</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.326976583950048</v>
       </c>
       <c r="E53">
-        <v>-22.17563588451083</v>
+        <v>-20.58388632776271</v>
       </c>
       <c r="F53">
-        <v>6.850237934084186</v>
+        <v>7.744429067444946</v>
       </c>
       <c r="G53">
-        <v>-4.449880868916318</v>
+        <v>-3.406476368030982</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.426691989391567</v>
       </c>
       <c r="E54">
-        <v>-21.41736555429647</v>
+        <v>-19.73688054936805</v>
       </c>
       <c r="F54">
-        <v>6.482021996600583</v>
+        <v>7.483403871883599</v>
       </c>
       <c r="G54">
-        <v>-5.015921255766445</v>
+        <v>-2.236403773722052</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.537558486148658</v>
       </c>
       <c r="E55">
-        <v>-21.99778459633358</v>
+        <v>-19.16665057384819</v>
       </c>
       <c r="F55">
-        <v>6.768461504079819</v>
+        <v>7.43322303135681</v>
       </c>
       <c r="G55">
-        <v>-5.514009384877491</v>
+        <v>-3.403738546870005</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.664632648932989</v>
       </c>
       <c r="E56">
-        <v>-21.61824413280272</v>
+        <v>-19.07179715728353</v>
       </c>
       <c r="F56">
-        <v>6.582183212742683</v>
+        <v>8.084793636111623</v>
       </c>
       <c r="G56">
-        <v>-5.515446161641535</v>
+        <v>-2.75656330994342</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.813738662627816</v>
       </c>
       <c r="E57">
-        <v>-20.78005529330099</v>
+        <v>-18.19770657584899</v>
       </c>
       <c r="F57">
-        <v>6.709690493586</v>
+        <v>7.348819019950763</v>
       </c>
       <c r="G57">
-        <v>-6.031321851935085</v>
+        <v>-3.744751221779251</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.988279984767534</v>
       </c>
       <c r="E58">
-        <v>-21.31222344478638</v>
+        <v>-18.20287356469174</v>
       </c>
       <c r="F58">
-        <v>7.276368350167113</v>
+        <v>7.574598839257797</v>
       </c>
       <c r="G58">
-        <v>-6.27808660588682</v>
+        <v>-3.242114403097246</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.187804405009243</v>
       </c>
       <c r="E59">
-        <v>-20.28232618664393</v>
+        <v>-17.3172127321676</v>
       </c>
       <c r="F59">
-        <v>6.610841411409934</v>
+        <v>7.632022924354664</v>
       </c>
       <c r="G59">
-        <v>-5.865529731328384</v>
+        <v>-2.948588193403306</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.411701232598935</v>
       </c>
       <c r="E60">
-        <v>-19.84311402111399</v>
+        <v>-16.8096568369139</v>
       </c>
       <c r="F60">
-        <v>6.671950074714454</v>
+        <v>7.227632182390807</v>
       </c>
       <c r="G60">
-        <v>-6.157228519884647</v>
+        <v>-4.032364797140054</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.652500853205081</v>
       </c>
       <c r="E61">
-        <v>-19.76854363962968</v>
+        <v>-17.25542170433294</v>
       </c>
       <c r="F61">
-        <v>6.566046615736148</v>
+        <v>7.584968342406041</v>
       </c>
       <c r="G61">
-        <v>-6.385189375173322</v>
+        <v>-4.44192231743991</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.905586745044919</v>
       </c>
       <c r="E62">
-        <v>-18.99506669369756</v>
+        <v>-18.22032177504329</v>
       </c>
       <c r="F62">
-        <v>6.634459822798554</v>
+        <v>7.483165302071593</v>
       </c>
       <c r="G62">
-        <v>-6.705050974632164</v>
+        <v>-4.393839954027535</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.158794558087454</v>
       </c>
       <c r="E63">
-        <v>-19.62351925953404</v>
+        <v>-16.87809566459182</v>
       </c>
       <c r="F63">
-        <v>6.823383919620231</v>
+        <v>7.494359859153025</v>
       </c>
       <c r="G63">
-        <v>-6.577028868083008</v>
+        <v>-4.369216116306436</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.406288720602689</v>
       </c>
       <c r="E64">
-        <v>-18.06123648315383</v>
+        <v>-15.43882888462998</v>
       </c>
       <c r="F64">
-        <v>6.58593737381217</v>
+        <v>6.983576921443211</v>
       </c>
       <c r="G64">
-        <v>-7.227498097821169</v>
+        <v>-5.42807424376909</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.635027505559314</v>
       </c>
       <c r="E65">
-        <v>-19.15104092394375</v>
+        <v>-16.78489514103996</v>
       </c>
       <c r="F65">
-        <v>6.259025491766956</v>
+        <v>7.15786045278781</v>
       </c>
       <c r="G65">
-        <v>-7.570046865860637</v>
+        <v>-4.772066471343729</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.840906604827229</v>
       </c>
       <c r="E66">
-        <v>-17.52217599422877</v>
+        <v>-17.20827123296507</v>
       </c>
       <c r="F66">
-        <v>6.362694015492509</v>
+        <v>7.233026510917838</v>
       </c>
       <c r="G66">
-        <v>-7.454141355985213</v>
+        <v>-4.951994621403118</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.013916533535969</v>
       </c>
       <c r="E67">
-        <v>-17.6503046378018</v>
+        <v>-15.99033362012812</v>
       </c>
       <c r="F67">
-        <v>6.282824487249386</v>
+        <v>6.938142626134463</v>
       </c>
       <c r="G67">
-        <v>-6.616881215284755</v>
+        <v>-5.339278791314758</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.153422390110771</v>
       </c>
       <c r="E68">
-        <v>-17.95071454652263</v>
+        <v>-15.03872009215628</v>
       </c>
       <c r="F68">
-        <v>6.349889112180034</v>
+        <v>7.135403412497916</v>
       </c>
       <c r="G68">
-        <v>-7.267532525027575</v>
+        <v>-5.010276775621987</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.253939807590546</v>
       </c>
       <c r="E69">
-        <v>-17.6433987149401</v>
+        <v>-14.87325870886402</v>
       </c>
       <c r="F69">
-        <v>5.962819532608715</v>
+        <v>6.806021338857554</v>
       </c>
       <c r="G69">
-        <v>-6.802026785114036</v>
+        <v>-5.456981927418005</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.317763092644157</v>
       </c>
       <c r="E70">
-        <v>-16.88863342360767</v>
+        <v>-15.50196939771893</v>
       </c>
       <c r="F70">
-        <v>6.233165518186361</v>
+        <v>6.678311936367954</v>
       </c>
       <c r="G70">
-        <v>-7.183133477049395</v>
+        <v>-4.453969392657318</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.342254992969016</v>
       </c>
       <c r="E71">
-        <v>-17.77140961818892</v>
+        <v>-16.47709476273861</v>
       </c>
       <c r="F71">
-        <v>6.056787874047485</v>
+        <v>6.250279588728199</v>
       </c>
       <c r="G71">
-        <v>-6.682075788589622</v>
+        <v>-5.214875111040025</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.328587256910648</v>
       </c>
       <c r="E72">
-        <v>-17.10997617615458</v>
+        <v>-16.14285262470646</v>
       </c>
       <c r="F72">
-        <v>5.664055574910628</v>
+        <v>6.40466739179236</v>
       </c>
       <c r="G72">
-        <v>-7.208065195505647</v>
+        <v>-5.300614929961609</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.275392601964445</v>
       </c>
       <c r="E73">
-        <v>-17.08222568743558</v>
+        <v>-15.47573141931849</v>
       </c>
       <c r="F73">
-        <v>5.855096978813862</v>
+        <v>6.453575859988448</v>
       </c>
       <c r="G73">
-        <v>-7.568014190899524</v>
+        <v>-4.184173173388873</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.180771873835326</v>
       </c>
       <c r="E74">
-        <v>-17.31139364306775</v>
+        <v>-15.42547441478136</v>
       </c>
       <c r="F74">
-        <v>5.702235028505657</v>
+        <v>6.47042485296139</v>
       </c>
       <c r="G74">
-        <v>-7.120739625270751</v>
+        <v>-4.386205836013976</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.046714920198612</v>
       </c>
       <c r="E75">
-        <v>-18.00787294544745</v>
+        <v>-17.21198911012537</v>
       </c>
       <c r="F75">
-        <v>5.44910417429299</v>
+        <v>6.754105896989303</v>
       </c>
       <c r="G75">
-        <v>-6.662338316084488</v>
+        <v>-4.161118534253388</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.871450150221767</v>
       </c>
       <c r="E76">
-        <v>-17.54381304303742</v>
+        <v>-16.3461448798588</v>
       </c>
       <c r="F76">
-        <v>5.529989280971945</v>
+        <v>5.970117449427378</v>
       </c>
       <c r="G76">
-        <v>-7.225650813410256</v>
+        <v>-3.796842655839683</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.660328754741199</v>
       </c>
       <c r="E77">
-        <v>-18.69081211054421</v>
+        <v>-16.58659326424407</v>
       </c>
       <c r="F77">
-        <v>5.427077885052551</v>
+        <v>6.313008538672594</v>
       </c>
       <c r="G77">
-        <v>-6.815093508357539</v>
+        <v>-4.041584666466924</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.411682050224369</v>
       </c>
       <c r="E78">
-        <v>-19.19491278013006</v>
+        <v>-15.55961687183657</v>
       </c>
       <c r="F78">
-        <v>5.367703823089494</v>
+        <v>5.858153654530192</v>
       </c>
       <c r="G78">
-        <v>-6.510665672202778</v>
+        <v>-4.493758839493818</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.132647349858955</v>
       </c>
       <c r="E79">
-        <v>-19.01418138248394</v>
+        <v>-17.09048562402557</v>
       </c>
       <c r="F79">
-        <v>5.35766566690237</v>
+        <v>6.036651919220235</v>
       </c>
       <c r="G79">
-        <v>-5.9692954707113</v>
+        <v>-3.134882522534713</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.821360131492729</v>
       </c>
       <c r="E80">
-        <v>-18.72432281820097</v>
+        <v>-17.40230275877173</v>
       </c>
       <c r="F80">
-        <v>5.162286931278078</v>
+        <v>6.155993154206754</v>
       </c>
       <c r="G80">
-        <v>-6.338192870697828</v>
+        <v>-3.441127848190534</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.485130481582102</v>
       </c>
       <c r="E81">
-        <v>-19.68139768582607</v>
+        <v>-16.87545103577134</v>
       </c>
       <c r="F81">
-        <v>5.189338097183898</v>
+        <v>5.869146089965341</v>
       </c>
       <c r="G81">
-        <v>-5.90425318250124</v>
+        <v>-2.484986017174847</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.122733601056929</v>
       </c>
       <c r="E82">
-        <v>-20.58043563056887</v>
+        <v>-17.55749356301459</v>
       </c>
       <c r="F82">
-        <v>4.993016679455222</v>
+        <v>5.786622472563649</v>
       </c>
       <c r="G82">
-        <v>-6.180293090656749</v>
+        <v>-2.620642241737563</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.741485138810519</v>
       </c>
       <c r="E83">
-        <v>-20.99552008658594</v>
+        <v>-17.0870213414097</v>
       </c>
       <c r="F83">
-        <v>4.937880545124886</v>
+        <v>5.111536173978164</v>
       </c>
       <c r="G83">
-        <v>-6.023340126639902</v>
+        <v>-2.268466407269894</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.342841536760552</v>
       </c>
       <c r="E84">
-        <v>-21.47785691009092</v>
+        <v>-19.98619115738633</v>
       </c>
       <c r="F84">
-        <v>4.867835454278966</v>
+        <v>5.447116092526271</v>
       </c>
       <c r="G84">
-        <v>-5.276974324265674</v>
+        <v>-1.993333588592144</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.934229360072293</v>
       </c>
       <c r="E85">
-        <v>-21.73946232504003</v>
+        <v>-20.49804910294732</v>
       </c>
       <c r="F85">
-        <v>4.725603114483485</v>
+        <v>5.485310456734551</v>
       </c>
       <c r="G85">
-        <v>-4.956324814968485</v>
+        <v>-1.995151078093204</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.519518350239657</v>
       </c>
       <c r="E86">
-        <v>-23.47977300008379</v>
+        <v>-20.57140132492357</v>
       </c>
       <c r="F86">
-        <v>4.610986887162534</v>
+        <v>5.216061229598211</v>
       </c>
       <c r="G86">
-        <v>-4.731893001224673</v>
+        <v>-1.148896185162546</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.105627412327234</v>
       </c>
       <c r="E87">
-        <v>-25.28848627501339</v>
+        <v>-22.08335011270852</v>
       </c>
       <c r="F87">
-        <v>4.441454871240393</v>
+        <v>5.459498528463318</v>
       </c>
       <c r="G87">
-        <v>-4.201705822564853</v>
+        <v>-1.704005150641999</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.698904268528207</v>
       </c>
       <c r="E88">
-        <v>-25.78851584646635</v>
+        <v>-23.7949321486476</v>
       </c>
       <c r="F88">
-        <v>4.485790751373028</v>
+        <v>4.660379121921857</v>
       </c>
       <c r="G88">
-        <v>-3.91282430826251</v>
+        <v>-1.065099656472514</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.305464612261651</v>
       </c>
       <c r="E89">
-        <v>-27.00021322212073</v>
+        <v>-24.13704930297908</v>
       </c>
       <c r="F89">
-        <v>3.957704875353538</v>
+        <v>4.622728166729814</v>
       </c>
       <c r="G89">
-        <v>-4.36370074743801</v>
+        <v>-1.748147964862641</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.933709109905318</v>
       </c>
       <c r="E90">
-        <v>-28.58575424100433</v>
+        <v>-26.44402151602465</v>
       </c>
       <c r="F90">
-        <v>3.834372566220331</v>
+        <v>4.386505947943091</v>
       </c>
       <c r="G90">
-        <v>-4.081288039119404</v>
+        <v>-0.5336809548720849</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.586542477582077</v>
       </c>
       <c r="E91">
-        <v>-30.05717545065763</v>
+        <v>-28.37817804944073</v>
       </c>
       <c r="F91">
-        <v>3.861867737054052</v>
+        <v>4.489404089984039</v>
       </c>
       <c r="G91">
-        <v>-3.959281193815103</v>
+        <v>-1.066526501599939</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.270904908442353</v>
       </c>
       <c r="E92">
-        <v>-31.38833170639735</v>
+        <v>-29.60461560799008</v>
       </c>
       <c r="F92">
-        <v>3.898899073428801</v>
+        <v>4.007516264018678</v>
       </c>
       <c r="G92">
-        <v>-2.689157292218319</v>
+        <v>-0.8370858324552106</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.98658409445207</v>
       </c>
       <c r="E93">
-        <v>-32.98896386491151</v>
+        <v>-31.26292241146593</v>
       </c>
       <c r="F93">
-        <v>3.099570918301835</v>
+        <v>3.920723241022957</v>
       </c>
       <c r="G93">
-        <v>-3.669740880950445</v>
+        <v>-0.9979353085717798</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.740227145543574</v>
       </c>
       <c r="E94">
-        <v>-35.32593042554688</v>
+        <v>-32.69917096350166</v>
       </c>
       <c r="F94">
-        <v>2.914601447461122</v>
+        <v>2.873769561442329</v>
       </c>
       <c r="G94">
-        <v>-3.412220164541618</v>
+        <v>-1.051235091754046</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.529611210245956</v>
       </c>
       <c r="E95">
-        <v>-37.60125766222684</v>
+        <v>-34.83256903207022</v>
       </c>
       <c r="F95">
-        <v>2.430414073585589</v>
+        <v>2.908928787486751</v>
       </c>
       <c r="G95">
-        <v>-3.887776720712385</v>
+        <v>-0.2724358747315777</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.362483468455828</v>
       </c>
       <c r="E96">
-        <v>-39.14236982262119</v>
+        <v>-37.03913591941772</v>
       </c>
       <c r="F96">
-        <v>2.131292261169492</v>
+        <v>2.464562691398595</v>
       </c>
       <c r="G96">
-        <v>-3.347515551976562</v>
+        <v>-0.9071369760661889</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.233396667161867</v>
       </c>
       <c r="E97">
-        <v>-41.45085001751131</v>
+        <v>-39.68666069902511</v>
       </c>
       <c r="F97">
-        <v>1.425773400939959</v>
+        <v>1.802203429589722</v>
       </c>
       <c r="G97">
-        <v>-3.860285950554276</v>
+        <v>-1.18126669944554</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.152167432560635</v>
       </c>
       <c r="E98">
-        <v>-43.78839169434565</v>
+        <v>-42.56908648235838</v>
       </c>
       <c r="F98">
-        <v>1.113193931697983</v>
+        <v>1.836058805342138</v>
       </c>
       <c r="G98">
-        <v>-4.597753006518944</v>
+        <v>-1.263384781547161</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.106937419205125</v>
       </c>
       <c r="E99">
-        <v>-47.01201988026085</v>
+        <v>-43.42321781460412</v>
       </c>
       <c r="F99">
-        <v>0.8005117448980589</v>
+        <v>1.175162440366608</v>
       </c>
       <c r="G99">
-        <v>-4.191492789576202</v>
+        <v>-1.181836113278294</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.115428337268291</v>
       </c>
       <c r="E100">
-        <v>-48.39665062132015</v>
+        <v>-47.56592923545706</v>
       </c>
       <c r="F100">
-        <v>0.5800533577866097</v>
+        <v>1.132756656282496</v>
       </c>
       <c r="G100">
-        <v>-3.875497907307228</v>
+        <v>-0.8349637727645378</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.152543719537979</v>
       </c>
       <c r="E101">
-        <v>-49.91184292861309</v>
+        <v>-48.99947881698422</v>
       </c>
       <c r="F101">
-        <v>-0.1450116596793808</v>
+        <v>0.2130766579375951</v>
       </c>
       <c r="G101">
-        <v>-4.725781734159178</v>
+        <v>-1.271608176666711</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.262054892821181</v>
       </c>
       <c r="E102">
-        <v>-52.98907913528233</v>
+        <v>-50.75752865683452</v>
       </c>
       <c r="F102">
-        <v>-0.4008479618295913</v>
+        <v>-0.1314786214198453</v>
       </c>
       <c r="G102">
-        <v>-4.420837452900292</v>
+        <v>-2.077726015479245</v>
       </c>
     </row>
   </sheetData>
